--- a/grupos/1DM - Estadisticos 20221.xlsx
+++ b/grupos/1DM - Estadisticos 20221.xlsx
@@ -308,12 +308,12 @@
     <t>CAMACHO</t>
   </si>
   <si>
+    <t>GALICIA</t>
+  </si>
+  <si>
     <t>GOMEZ</t>
   </si>
   <si>
-    <t>GALICIA</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
@@ -485,13 +485,13 @@
     <t>GUADALUPE</t>
   </si>
   <si>
+    <t>AYLIN VALENTINA</t>
+  </si>
+  <si>
+    <t>MIRIAM ANELI</t>
+  </si>
+  <si>
     <t>HEIDY IDARA</t>
-  </si>
-  <si>
-    <t>AYLIN VALENTINA</t>
-  </si>
-  <si>
-    <t>MIRIAM ANELI</t>
   </si>
   <si>
     <t>MARLEN FERNANDA</t>
@@ -5099,13 +5099,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>22330051920338</v>
+        <v>22330051920090</v>
       </c>
       <c r="B11" t="s">
         <v>96</v>
       </c>
       <c r="C11" t="s">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="D11" t="s">
         <v>155</v>
@@ -5116,13 +5116,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>22330051920090</v>
+        <v>22330051920092</v>
       </c>
       <c r="B12" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="C12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D12" t="s">
         <v>156</v>
@@ -5133,13 +5133,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>22330051920092</v>
+        <v>22330051920338</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="C13" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="D13" t="s">
         <v>157</v>
@@ -5292,7 +5292,7 @@
         <v>101</v>
       </c>
       <c r="C22" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D22" t="s">
         <v>166</v>
@@ -5829,7 +5829,7 @@
         <v>101</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D6" t="s">
         <v>166</v>

--- a/grupos/1DM - Estadisticos 20221.xlsx
+++ b/grupos/1DM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="190">
   <si>
     <t>Materia</t>
   </si>
@@ -218,18 +218,18 @@
     <t>González Altamirano Victorino Juventino</t>
   </si>
   <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
+    <t>Moreno Aroyo Anél</t>
+  </si>
+  <si>
     <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
-    <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
-    <t>Moreno Aroyo Anél</t>
-  </si>
-  <si>
-    <t>García Sánchez Magda Bexabe</t>
-  </si>
-  <si>
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
@@ -245,337 +245,337 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>ANGEL</t>
+  </si>
+  <si>
+    <t>CAMACHO</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
+    <t>GALICIA</t>
+  </si>
+  <si>
     <t>GAMBOA</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>JALAPA</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>LARRACILLA</t>
+  </si>
+  <si>
+    <t>LOMAN</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>DE LUNA</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>MENDOZA</t>
   </si>
   <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>RANGEL</t>
+  </si>
+  <si>
     <t>REYES</t>
   </si>
   <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SHEIKH</t>
+  </si>
+  <si>
     <t>TLAXCALA</t>
   </si>
   <si>
+    <t>TEPOLE</t>
+  </si>
+  <si>
+    <t>TELE</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
     <t>DELGADO</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>AGUIRRE</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
+    <t>PRADO</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
   </si>
   <si>
     <t>LUGO</t>
   </si>
   <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
     <t>BAUTISTA</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
+    <t>FALFAN</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>ONOFRE</t>
+  </si>
+  <si>
+    <t>TELLEZ</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>BAZAN</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>CUAHUA</t>
+  </si>
+  <si>
+    <t>SOTO</t>
+  </si>
+  <si>
+    <t>OYOLA</t>
+  </si>
+  <si>
+    <t>SAAVEDRA</t>
+  </si>
+  <si>
+    <t>GIL</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>OLTEHUA</t>
+  </si>
+  <si>
+    <t>TEHUINTLE</t>
+  </si>
+  <si>
+    <t>SAUL</t>
+  </si>
+  <si>
+    <t>IRAIS</t>
+  </si>
+  <si>
+    <t>GUADALUPE</t>
   </si>
   <si>
     <t>DAMON</t>
   </si>
   <si>
+    <t>AYLIN VALENTINA</t>
+  </si>
+  <si>
     <t>DIEGO ARMANDO</t>
   </si>
   <si>
+    <t>MIRIAM ANELI</t>
+  </si>
+  <si>
+    <t>HEIDY IDARA</t>
+  </si>
+  <si>
+    <t>MARLEN FERNANDA</t>
+  </si>
+  <si>
+    <t>AMERICA</t>
+  </si>
+  <si>
+    <t>LINDA PAOLA</t>
+  </si>
+  <si>
+    <t>MARIO</t>
+  </si>
+  <si>
+    <t>MARCO</t>
+  </si>
+  <si>
+    <t>ANETTE</t>
+  </si>
+  <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
+    <t>ESTRELLA</t>
+  </si>
+  <si>
+    <t>MONSERRAT</t>
+  </si>
+  <si>
+    <t>RAFAEL</t>
+  </si>
+  <si>
     <t>ZAYRA</t>
   </si>
   <si>
+    <t>ALEJANDRA JANETTE</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>ESMERALDA AIMEE</t>
+  </si>
+  <si>
+    <t>ELISA MARELI</t>
+  </si>
+  <si>
     <t>VALERIA</t>
   </si>
   <si>
+    <t>JESUA JEHIELI</t>
+  </si>
+  <si>
+    <t>ANDREA</t>
+  </si>
+  <si>
+    <t>BARUCH BOSET</t>
+  </si>
+  <si>
+    <t>AHILY</t>
+  </si>
+  <si>
+    <t>MAYTE</t>
+  </si>
+  <si>
+    <t>YUSEF ABRIL</t>
+  </si>
+  <si>
     <t>BETZABE</t>
   </si>
   <si>
+    <t>ILSE LEILANI</t>
+  </si>
+  <si>
+    <t>ILEANA</t>
+  </si>
+  <si>
+    <t>IAN YASSEL</t>
+  </si>
+  <si>
+    <t>DANA DANIELA</t>
+  </si>
+  <si>
+    <t>VICTORIA</t>
+  </si>
+  <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>IVON</t>
+  </si>
+  <si>
+    <t>TANIA REYNA</t>
+  </si>
+  <si>
     <t>CARLOS ROBERTO</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>ANGEL</t>
-  </si>
-  <si>
-    <t>CAMACHO</t>
-  </si>
-  <si>
-    <t>GALICIA</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>JALAPA</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>LARRACILLA</t>
-  </si>
-  <si>
-    <t>LOMAN</t>
-  </si>
-  <si>
-    <t>DE LUNA</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>RANGEL</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SHEIKH</t>
-  </si>
-  <si>
-    <t>TEPOLE</t>
-  </si>
-  <si>
-    <t>TELE</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>AGUIRRE</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>PRADO</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>FALFAN</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ONOFRE</t>
-  </si>
-  <si>
-    <t>TELLEZ</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>BAZAN</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>CUAHUA</t>
-  </si>
-  <si>
-    <t>SOTO</t>
-  </si>
-  <si>
-    <t>OYOLA</t>
-  </si>
-  <si>
-    <t>SAAVEDRA</t>
-  </si>
-  <si>
-    <t>GIL</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>OLTEHUA</t>
-  </si>
-  <si>
-    <t>TEHUINTLE</t>
-  </si>
-  <si>
-    <t>SAUL</t>
-  </si>
-  <si>
-    <t>IRAIS</t>
-  </si>
-  <si>
-    <t>GUADALUPE</t>
-  </si>
-  <si>
-    <t>AYLIN VALENTINA</t>
-  </si>
-  <si>
-    <t>MIRIAM ANELI</t>
-  </si>
-  <si>
-    <t>HEIDY IDARA</t>
-  </si>
-  <si>
-    <t>MARLEN FERNANDA</t>
-  </si>
-  <si>
-    <t>AMERICA</t>
-  </si>
-  <si>
-    <t>LINDA PAOLA</t>
-  </si>
-  <si>
-    <t>MARIO</t>
-  </si>
-  <si>
-    <t>MARCO</t>
-  </si>
-  <si>
-    <t>ANETTE</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
-    <t>ESTRELLA</t>
-  </si>
-  <si>
-    <t>MONSERRAT</t>
-  </si>
-  <si>
-    <t>RAFAEL</t>
-  </si>
-  <si>
-    <t>ALEJANDRA JANETTE</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>ESMERALDA AIMEE</t>
-  </si>
-  <si>
-    <t>ELISA MARELI</t>
-  </si>
-  <si>
-    <t>JESUA JEHIELI</t>
-  </si>
-  <si>
-    <t>ANDREA</t>
-  </si>
-  <si>
-    <t>BARUCH BOSET</t>
-  </si>
-  <si>
-    <t>AHILY</t>
-  </si>
-  <si>
-    <t>MAYTE</t>
-  </si>
-  <si>
-    <t>YUSEF ABRIL</t>
-  </si>
-  <si>
-    <t>ILSE LEILANI</t>
-  </si>
-  <si>
-    <t>ILEANA</t>
-  </si>
-  <si>
-    <t>IAN YASSEL</t>
-  </si>
-  <si>
-    <t>DANA DANIELA</t>
-  </si>
-  <si>
-    <t>VICTORIA</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>IVON</t>
-  </si>
-  <si>
-    <t>TANIA REYNA</t>
   </si>
   <si>
     <t>JESUS</t>
@@ -1091,19 +1091,19 @@
         <v>7</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K4">
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M4">
         <v>-1</v>
@@ -1130,16 +1130,16 @@
         <v>9</v>
       </c>
       <c r="U4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W4">
         <v>8</v>
       </c>
       <c r="X4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y4">
         <v>7</v>
@@ -1168,19 +1168,19 @@
         <v>10</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K5">
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M5">
         <v>-1</v>
@@ -1245,19 +1245,19 @@
         <v>8</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K6">
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M6">
         <v>-1</v>
@@ -1287,7 +1287,7 @@
         <v>9</v>
       </c>
       <c r="V6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W6">
         <v>6</v>
@@ -1316,25 +1316,25 @@
         <v>6</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G7">
         <v>5</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K7">
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M7">
         <v>-1</v>
@@ -1361,7 +1361,7 @@
         <v>6</v>
       </c>
       <c r="U7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V7">
         <v>6</v>
@@ -1370,7 +1370,7 @@
         <v>6</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y7">
         <v>5</v>
@@ -1399,19 +1399,19 @@
         <v>7</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K8">
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M8">
         <v>-1</v>
@@ -1438,10 +1438,10 @@
         <v>8</v>
       </c>
       <c r="U8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W8">
         <v>9</v>
@@ -1476,19 +1476,19 @@
         <v>8</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K9">
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M9">
         <v>-1</v>
@@ -1512,13 +1512,13 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U9">
         <v>10</v>
       </c>
       <c r="V9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W9">
         <v>10</v>
@@ -1553,19 +1553,19 @@
         <v>8</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K10">
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M10">
         <v>-1</v>
@@ -1589,7 +1589,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U10">
         <v>10</v>
@@ -1624,25 +1624,25 @@
         <v>5</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G11">
         <v>5</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K11">
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M11">
         <v>-1</v>
@@ -1666,10 +1666,10 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V11">
         <v>8</v>
@@ -1678,7 +1678,7 @@
         <v>5</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y11">
         <v>5</v>
@@ -1707,19 +1707,19 @@
         <v>8</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K12">
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M12">
         <v>-1</v>
@@ -1749,7 +1749,7 @@
         <v>10</v>
       </c>
       <c r="V12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W12">
         <v>10</v>
@@ -1784,19 +1784,19 @@
         <v>7</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K13">
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M13">
         <v>-1</v>
@@ -1820,7 +1820,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U13">
         <v>10</v>
@@ -1861,19 +1861,19 @@
         <v>7</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M14">
         <v>-1</v>
@@ -1938,19 +1938,19 @@
         <v>8</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K15">
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M15">
         <v>-1</v>
@@ -1974,7 +1974,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U15">
         <v>10</v>
@@ -2015,19 +2015,19 @@
         <v>7</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K16">
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M16">
         <v>-1</v>
@@ -2063,7 +2063,7 @@
         <v>10</v>
       </c>
       <c r="X16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y16">
         <v>7</v>
@@ -2092,19 +2092,19 @@
         <v>8</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K17">
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M17">
         <v>-1</v>
@@ -2128,7 +2128,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U17">
         <v>10</v>
@@ -2169,19 +2169,19 @@
         <v>6</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K18">
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M18">
         <v>-1</v>
@@ -2208,7 +2208,7 @@
         <v>6</v>
       </c>
       <c r="U18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V18">
         <v>8</v>
@@ -2217,7 +2217,7 @@
         <v>7</v>
       </c>
       <c r="X18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y18">
         <v>6</v>
@@ -2246,19 +2246,19 @@
         <v>6</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K19">
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M19">
         <v>-1</v>
@@ -2285,16 +2285,16 @@
         <v>6</v>
       </c>
       <c r="U19">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W19">
         <v>6</v>
       </c>
       <c r="X19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y19">
         <v>6</v>
@@ -2323,19 +2323,19 @@
         <v>7</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K20">
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M20">
         <v>-1</v>
@@ -2359,10 +2359,10 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U20">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V20">
         <v>7</v>
@@ -2371,7 +2371,7 @@
         <v>8</v>
       </c>
       <c r="X20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y20">
         <v>7</v>
@@ -2400,19 +2400,19 @@
         <v>6</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K21">
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M21">
         <v>-1</v>
@@ -2436,10 +2436,10 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V21">
         <v>5</v>
@@ -2477,19 +2477,19 @@
         <v>6</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M22">
         <v>-1</v>
@@ -2513,7 +2513,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U22">
         <v>10</v>
@@ -2542,22 +2542,22 @@
         <v>6</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E23">
         <v>6</v>
       </c>
       <c r="F23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G23">
         <v>5</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J23">
         <v>-1</v>
@@ -2566,7 +2566,7 @@
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M23">
         <v>-1</v>
@@ -2593,16 +2593,16 @@
         <v>6</v>
       </c>
       <c r="U23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W23">
         <v>6</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y23">
         <v>5</v>
@@ -2631,19 +2631,19 @@
         <v>10</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K24">
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M24">
         <v>-1</v>
@@ -2667,7 +2667,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U24">
         <v>10</v>
@@ -2679,7 +2679,7 @@
         <v>9</v>
       </c>
       <c r="X24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y24">
         <v>10</v>
@@ -2708,19 +2708,19 @@
         <v>9</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K25">
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M25">
         <v>-1</v>
@@ -2750,13 +2750,13 @@
         <v>10</v>
       </c>
       <c r="V25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W25">
         <v>9</v>
       </c>
       <c r="X25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y25">
         <v>9</v>
@@ -2785,19 +2785,19 @@
         <v>8</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K26">
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M26">
         <v>-1</v>
@@ -2821,7 +2821,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U26">
         <v>10</v>
@@ -2862,19 +2862,19 @@
         <v>8</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K27">
         <v>-1</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M27">
         <v>-1</v>
@@ -2904,7 +2904,7 @@
         <v>10</v>
       </c>
       <c r="V27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W27">
         <v>10</v>
@@ -2927,22 +2927,22 @@
         <v>5</v>
       </c>
       <c r="D28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E28">
         <v>6</v>
       </c>
       <c r="F28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G28">
         <v>5</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J28">
         <v>-1</v>
@@ -2951,7 +2951,7 @@
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M28">
         <v>-1</v>
@@ -2978,16 +2978,16 @@
         <v>6</v>
       </c>
       <c r="U28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W28">
         <v>6</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y28">
         <v>5</v>
@@ -3016,19 +3016,19 @@
         <v>8</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K29">
         <v>-1</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M29">
         <v>-1</v>
@@ -3058,7 +3058,7 @@
         <v>10</v>
       </c>
       <c r="V29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W29">
         <v>10</v>
@@ -3093,19 +3093,19 @@
         <v>6</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K30">
         <v>-1</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M30">
         <v>-1</v>
@@ -3135,7 +3135,7 @@
         <v>10</v>
       </c>
       <c r="V30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W30">
         <v>9</v>
@@ -3170,19 +3170,19 @@
         <v>6</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K31">
         <v>-1</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M31">
         <v>-1</v>
@@ -3206,13 +3206,13 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U31">
         <v>10</v>
       </c>
       <c r="V31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W31">
         <v>6</v>
@@ -3247,19 +3247,19 @@
         <v>8</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K32">
         <v>-1</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M32">
         <v>-1</v>
@@ -3295,7 +3295,7 @@
         <v>9</v>
       </c>
       <c r="X32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y32">
         <v>8</v>
@@ -3324,19 +3324,19 @@
         <v>7</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K33">
         <v>-1</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M33">
         <v>-1</v>
@@ -3360,7 +3360,7 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U33">
         <v>10</v>
@@ -3372,7 +3372,7 @@
         <v>10</v>
       </c>
       <c r="X33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y33">
         <v>7</v>
@@ -3395,25 +3395,25 @@
         <v>9</v>
       </c>
       <c r="F34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G34">
         <v>7</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K34">
         <v>-1</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M34">
         <v>-1</v>
@@ -3437,19 +3437,19 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U34">
         <v>10</v>
       </c>
       <c r="V34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W34">
         <v>9</v>
       </c>
       <c r="X34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y34">
         <v>7</v>
@@ -3478,19 +3478,19 @@
         <v>7</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K35">
         <v>-1</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M35">
         <v>-1</v>
@@ -3555,19 +3555,19 @@
         <v>7</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K36">
         <v>-1</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M36">
         <v>-1</v>
@@ -3594,7 +3594,7 @@
         <v>6</v>
       </c>
       <c r="U36">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V36">
         <v>6</v>
@@ -3632,19 +3632,19 @@
         <v>9</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K37">
         <v>-1</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M37">
         <v>-1</v>
@@ -3671,16 +3671,16 @@
         <v>10</v>
       </c>
       <c r="U37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W37">
         <v>9</v>
       </c>
       <c r="X37">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y37">
         <v>9</v>
@@ -3709,19 +3709,19 @@
         <v>7</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K38">
         <v>-1</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M38">
         <v>-1</v>
@@ -3745,13 +3745,13 @@
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U38">
         <v>9</v>
       </c>
       <c r="V38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W38">
         <v>6</v>
@@ -3786,19 +3786,19 @@
         <v>10</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K39">
         <v>-1</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M39">
         <v>-1</v>
@@ -3863,19 +3863,19 @@
         <v>9</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K40">
         <v>-1</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M40">
         <v>-1</v>
@@ -3899,7 +3899,7 @@
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U40">
         <v>10</v>
@@ -3940,19 +3940,19 @@
         <v>5</v>
       </c>
       <c r="H41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K41">
         <v>-1</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M41">
         <v>-1</v>
@@ -3976,10 +3976,10 @@
         <v>-1</v>
       </c>
       <c r="T41">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U41">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V41">
         <v>9</v>
@@ -4017,19 +4017,19 @@
         <v>8</v>
       </c>
       <c r="H42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K42">
         <v>-1</v>
       </c>
       <c r="L42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M42">
         <v>-1</v>
@@ -4094,19 +4094,19 @@
         <v>5</v>
       </c>
       <c r="H43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K43">
         <v>-1</v>
       </c>
       <c r="L43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M43">
         <v>-1</v>
@@ -4133,10 +4133,10 @@
         <v>6</v>
       </c>
       <c r="U43">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W43">
         <v>5</v>
@@ -4171,19 +4171,19 @@
         <v>7</v>
       </c>
       <c r="H44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K44">
         <v>-1</v>
       </c>
       <c r="L44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M44">
         <v>-1</v>
@@ -4207,7 +4207,7 @@
         <v>-1</v>
       </c>
       <c r="T44">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U44">
         <v>10</v>
@@ -4236,22 +4236,22 @@
         <v>5</v>
       </c>
       <c r="D45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E45">
         <v>6</v>
       </c>
       <c r="F45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G45">
         <v>5</v>
       </c>
       <c r="H45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J45">
         <v>-1</v>
@@ -4260,7 +4260,7 @@
         <v>-1</v>
       </c>
       <c r="L45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M45">
         <v>-1</v>
@@ -4290,13 +4290,13 @@
         <v>5</v>
       </c>
       <c r="V45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W45">
         <v>6</v>
       </c>
       <c r="X45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y45">
         <v>5</v>
@@ -4325,19 +4325,19 @@
         <v>9</v>
       </c>
       <c r="H46">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J46">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K46">
         <v>-1</v>
       </c>
       <c r="L46">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M46">
         <v>-1</v>
@@ -4361,7 +4361,7 @@
         <v>-1</v>
       </c>
       <c r="T46">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U46">
         <v>10</v>
@@ -4402,19 +4402,19 @@
         <v>10</v>
       </c>
       <c r="H47">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I47">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J47">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K47">
         <v>-1</v>
       </c>
       <c r="L47">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M47">
         <v>-1</v>
@@ -4438,7 +4438,7 @@
         <v>-1</v>
       </c>
       <c r="T47">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U47">
         <v>10</v>
@@ -4541,7 +4541,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
@@ -4553,27 +4553,27 @@
         <v>38</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F3">
         <v>86.36</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>13.64</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>13.64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
@@ -4582,25 +4582,25 @@
         <v>44</v>
       </c>
       <c r="D4">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>90.91</v>
+        <v>95.45</v>
       </c>
       <c r="G4">
-        <v>2.27</v>
+        <v>4.55</v>
       </c>
       <c r="H4">
         <v>8.1</v>
       </c>
       <c r="I4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>6.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -4614,16 +4614,16 @@
         <v>44</v>
       </c>
       <c r="D5">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>93.18000000000001</v>
+        <v>95.45</v>
       </c>
       <c r="G5">
-        <v>6.82</v>
+        <v>4.55</v>
       </c>
       <c r="H5">
         <v>9.1</v>
@@ -4637,7 +4637,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>69</v>
@@ -4658,7 +4658,7 @@
         <v>4.55</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>7.3</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4690,7 +4690,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>7.5</v>
+        <v>8.1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4706,7 +4706,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4731,186 +4731,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>22330051920337</v>
-      </c>
-      <c r="B2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>22330051920091</v>
-      </c>
-      <c r="B3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D3" t="s">
-        <v>88</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>22330051920100</v>
-      </c>
-      <c r="B4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D4" t="s">
-        <v>89</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>22330051920100</v>
-      </c>
-      <c r="B5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C5" t="s">
-        <v>83</v>
-      </c>
-      <c r="D5" t="s">
-        <v>89</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>22330051920105</v>
-      </c>
-      <c r="B6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" t="s">
-        <v>84</v>
-      </c>
-      <c r="D6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>22330051920105</v>
-      </c>
-      <c r="B7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C7" t="s">
-        <v>84</v>
-      </c>
-      <c r="D7" t="s">
-        <v>90</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>22330051920112</v>
-      </c>
-      <c r="B8" t="s">
-        <v>79</v>
-      </c>
-      <c r="C8" t="s">
-        <v>85</v>
-      </c>
-      <c r="D8" t="s">
-        <v>91</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920281</v>
-      </c>
-      <c r="B9" t="s">
-        <v>80</v>
-      </c>
-      <c r="C9" t="s">
-        <v>86</v>
-      </c>
-      <c r="D9" t="s">
-        <v>92</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920281</v>
-      </c>
-      <c r="B10" t="s">
-        <v>80</v>
-      </c>
-      <c r="C10" t="s">
-        <v>86</v>
-      </c>
-      <c r="D10" t="s">
-        <v>92</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -4946,53 +4766,53 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>22330051920100</v>
+        <v>22330051920086</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>146</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>22330051920105</v>
+        <v>22330051920085</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>147</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920281</v>
+        <v>22330051920087</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="D4" t="s">
-        <v>92</v>
+        <v>148</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -5000,61 +4820,61 @@
         <v>22330051920337</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
+        <v>149</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>22330051920091</v>
+        <v>22330051920090</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="D6" t="s">
-        <v>88</v>
+        <v>150</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>22330051920112</v>
+        <v>22330051920091</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D7" t="s">
-        <v>91</v>
+        <v>151</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>22330051920086</v>
+        <v>22330051920092</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D8" t="s">
         <v>152</v>
@@ -5065,13 +4885,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>22330051920085</v>
+        <v>22330051920338</v>
       </c>
       <c r="B9" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
-        <v>123</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
         <v>153</v>
@@ -5082,13 +4902,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>22330051920087</v>
+        <v>22330051920093</v>
       </c>
       <c r="B10" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="C10" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D10" t="s">
         <v>154</v>
@@ -5099,13 +4919,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>22330051920090</v>
+        <v>22330051920094</v>
       </c>
       <c r="B11" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D11" t="s">
         <v>155</v>
@@ -5116,13 +4936,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>22330051920092</v>
+        <v>22330051920095</v>
       </c>
       <c r="B12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="D12" t="s">
         <v>156</v>
@@ -5133,13 +4953,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>22330051920338</v>
+        <v>22330051920096</v>
       </c>
       <c r="B13" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="C13" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="D13" t="s">
         <v>157</v>
@@ -5150,13 +4970,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>22330051920093</v>
+        <v>22330051920097</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C14" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D14" t="s">
         <v>158</v>
@@ -5167,13 +4987,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>22330051920094</v>
+        <v>22330051920098</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C15" t="s">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="D15" t="s">
         <v>159</v>
@@ -5184,13 +5004,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>22330051920095</v>
+        <v>22330051920339</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C16" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="D16" t="s">
         <v>160</v>
@@ -5201,13 +5021,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>22330051920096</v>
+        <v>22330051920088</v>
       </c>
       <c r="B17" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="C17" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D17" t="s">
         <v>161</v>
@@ -5218,13 +5038,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>22330051920097</v>
+        <v>22330051920340</v>
       </c>
       <c r="B18" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="C18" t="s">
-        <v>129</v>
+        <v>82</v>
       </c>
       <c r="D18" t="s">
         <v>162</v>
@@ -5235,13 +5055,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>22330051920098</v>
+        <v>22330051920099</v>
       </c>
       <c r="B19" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="C19" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="D19" t="s">
         <v>163</v>
@@ -5252,13 +5072,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>22330051920339</v>
+        <v>22330051920100</v>
       </c>
       <c r="B20" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s">
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="D20" t="s">
         <v>164</v>
@@ -5269,13 +5089,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>22330051920088</v>
+        <v>22330051920101</v>
       </c>
       <c r="B21" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21" t="s">
         <v>100</v>
-      </c>
-      <c r="C21" t="s">
-        <v>131</v>
       </c>
       <c r="D21" t="s">
         <v>165</v>
@@ -5286,13 +5106,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>22330051920340</v>
+        <v>22330051920089</v>
       </c>
       <c r="B22" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="C22" t="s">
-        <v>97</v>
+        <v>126</v>
       </c>
       <c r="D22" t="s">
         <v>166</v>
@@ -5303,13 +5123,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>22330051920099</v>
+        <v>22330051920102</v>
       </c>
       <c r="B23" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="C23" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D23" t="s">
         <v>167</v>
@@ -5320,13 +5140,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>22330051920101</v>
+        <v>22330051920103</v>
       </c>
       <c r="B24" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="C24" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="D24" t="s">
         <v>168</v>
@@ -5337,13 +5157,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>22330051920089</v>
+        <v>22330051920105</v>
       </c>
       <c r="B25" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="C25" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D25" t="s">
         <v>169</v>
@@ -5354,13 +5174,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>22330051920102</v>
+        <v>22330051920104</v>
       </c>
       <c r="B26" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="C26" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D26" t="s">
         <v>170</v>
@@ -5371,13 +5191,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>22330051920103</v>
+        <v>22330051920106</v>
       </c>
       <c r="B27" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="C27" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D27" t="s">
         <v>171</v>
@@ -5388,13 +5208,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>22330051920104</v>
+        <v>22330051920108</v>
       </c>
       <c r="B28" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="C28" t="s">
-        <v>136</v>
+        <v>101</v>
       </c>
       <c r="D28" t="s">
         <v>172</v>
@@ -5405,13 +5225,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>22330051920106</v>
+        <v>22330051920107</v>
       </c>
       <c r="B29" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="C29" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="D29" t="s">
         <v>173</v>
@@ -5422,13 +5242,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>22330051920108</v>
+        <v>22330051920109</v>
       </c>
       <c r="B30" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="C30" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="D30" t="s">
         <v>174</v>
@@ -5439,13 +5259,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>22330051920107</v>
+        <v>22330051920111</v>
       </c>
       <c r="B31" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="C31" t="s">
-        <v>84</v>
+        <v>133</v>
       </c>
       <c r="D31" t="s">
         <v>175</v>
@@ -5456,13 +5276,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>22330051920109</v>
+        <v>22330051920112</v>
       </c>
       <c r="B32" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="C32" t="s">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="D32" t="s">
         <v>176</v>
@@ -5473,13 +5293,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>22330051920111</v>
+        <v>22330051920113</v>
       </c>
       <c r="B33" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="C33" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="D33" t="s">
         <v>177</v>
@@ -5490,13 +5310,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>22330051920113</v>
+        <v>22330051920114</v>
       </c>
       <c r="B34" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C34" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D34" t="s">
         <v>178</v>
@@ -5507,13 +5327,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>22330051920114</v>
+        <v>22330051920115</v>
       </c>
       <c r="B35" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="C35" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D35" t="s">
         <v>179</v>
@@ -5524,13 +5344,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>22330051920115</v>
+        <v>22330051920117</v>
       </c>
       <c r="B36" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="C36" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D36" t="s">
         <v>180</v>
@@ -5541,13 +5361,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>22330051920117</v>
+        <v>22330051920118</v>
       </c>
       <c r="B37" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="C37" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D37" t="s">
         <v>181</v>
@@ -5558,13 +5378,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>22330051920118</v>
+        <v>22330051920116</v>
       </c>
       <c r="B38" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="C38" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D38" t="s">
         <v>182</v>
@@ -5575,13 +5395,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>22330051920116</v>
+        <v>22330051920119</v>
       </c>
       <c r="B39" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="C39" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="D39" t="s">
         <v>183</v>
@@ -5592,13 +5412,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>22330051920119</v>
+        <v>22330051920120</v>
       </c>
       <c r="B40" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C40" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D40" t="s">
         <v>184</v>
@@ -5609,13 +5429,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
-        <v>22330051920120</v>
+        <v>21330051920281</v>
       </c>
       <c r="B41" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="C41" t="s">
-        <v>147</v>
+        <v>119</v>
       </c>
       <c r="D41" t="s">
         <v>185</v>
@@ -5629,10 +5449,10 @@
         <v>22330051920122</v>
       </c>
       <c r="B42" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="C42" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D42" t="s">
         <v>186</v>
@@ -5646,10 +5466,10 @@
         <v>22330051920121</v>
       </c>
       <c r="B43" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="C43" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D43" t="s">
         <v>187</v>
@@ -5663,10 +5483,10 @@
         <v>22330051920123</v>
       </c>
       <c r="B44" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="C44" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D44" t="s">
         <v>188</v>
@@ -5680,10 +5500,10 @@
         <v>22330051920341</v>
       </c>
       <c r="B45" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="C45" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="D45" t="s">
         <v>189</v>
@@ -5699,7 +5519,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5734,42 +5554,42 @@
         <v>22330051920337</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>149</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920337</v>
+        <v>22330051920098</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>122</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>159</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5777,22 +5597,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920121</v>
+        <v>22330051920340</v>
       </c>
       <c r="B4" t="s">
-        <v>119</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>149</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>187</v>
+        <v>162</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5800,16 +5620,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920121</v>
+        <v>22330051920119</v>
       </c>
       <c r="B5" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="C5" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="D5" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -5818,75 +5638,6 @@
         <v>65</v>
       </c>
       <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920340</v>
-      </c>
-      <c r="B6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C6" t="s">
-        <v>97</v>
-      </c>
-      <c r="D6" t="s">
-        <v>166</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>67</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920112</v>
-      </c>
-      <c r="B7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C7" t="s">
-        <v>85</v>
-      </c>
-      <c r="D7" t="s">
-        <v>91</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>66</v>
-      </c>
-      <c r="G7">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920119</v>
-      </c>
-      <c r="B8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C8" t="s">
-        <v>146</v>
-      </c>
-      <c r="D8" t="s">
-        <v>184</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>65</v>
-      </c>
-      <c r="G8">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1DM - Estadisticos 20221.xlsx
+++ b/grupos/1DM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="190">
   <si>
     <t>Materia</t>
   </si>
@@ -1100,13 +1100,13 @@
         <v>7</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L4">
         <v>8</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1136,7 +1136,7 @@
         <v>8</v>
       </c>
       <c r="W4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X4">
         <v>7</v>
@@ -1177,13 +1177,13 @@
         <v>9</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L5">
         <v>9</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1254,13 +1254,13 @@
         <v>7</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L6">
         <v>7</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1290,7 +1290,7 @@
         <v>8</v>
       </c>
       <c r="W6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X6">
         <v>7</v>
@@ -1331,13 +1331,13 @@
         <v>6</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L7">
         <v>7</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1367,7 +1367,7 @@
         <v>6</v>
       </c>
       <c r="W7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X7">
         <v>7</v>
@@ -1408,13 +1408,13 @@
         <v>6</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
         <v>6</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1485,13 +1485,13 @@
         <v>7</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
         <v>8</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1562,13 +1562,13 @@
         <v>9</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L10">
         <v>7</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1639,13 +1639,13 @@
         <v>7</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L11">
         <v>6</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1716,13 +1716,13 @@
         <v>6</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L12">
         <v>8</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1793,13 +1793,13 @@
         <v>8</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L13">
         <v>7</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1870,13 +1870,13 @@
         <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L14">
         <v>6</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1906,7 +1906,7 @@
         <v>8</v>
       </c>
       <c r="W14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X14">
         <v>6</v>
@@ -1947,13 +1947,13 @@
         <v>8</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
         <v>6</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -2024,13 +2024,13 @@
         <v>7</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L16">
         <v>7</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -2060,7 +2060,7 @@
         <v>8</v>
       </c>
       <c r="W16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X16">
         <v>7</v>
@@ -2101,13 +2101,13 @@
         <v>7</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L17">
         <v>7</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2137,13 +2137,13 @@
         <v>8</v>
       </c>
       <c r="W17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X17">
         <v>8</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2178,13 +2178,13 @@
         <v>7</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
         <v>7</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2214,13 +2214,13 @@
         <v>8</v>
       </c>
       <c r="W18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X18">
         <v>7</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2255,13 +2255,13 @@
         <v>5</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
         <v>7</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2291,13 +2291,13 @@
         <v>5</v>
       </c>
       <c r="W19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X19">
         <v>7</v>
       </c>
       <c r="Y19">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2332,13 +2332,13 @@
         <v>6</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
         <v>7</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2368,13 +2368,13 @@
         <v>7</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X20">
         <v>7</v>
       </c>
       <c r="Y20">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2409,13 +2409,13 @@
         <v>6</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
         <v>6</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2445,7 +2445,7 @@
         <v>5</v>
       </c>
       <c r="W21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X21">
         <v>6</v>
@@ -2486,13 +2486,13 @@
         <v>8</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L22">
         <v>8</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2522,13 +2522,13 @@
         <v>9</v>
       </c>
       <c r="W22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X22">
         <v>9</v>
       </c>
       <c r="Y22">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2560,16 +2560,16 @@
         <v>5</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L23">
         <v>7</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2640,13 +2640,13 @@
         <v>10</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
         <v>8</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2676,13 +2676,13 @@
         <v>10</v>
       </c>
       <c r="W24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X24">
         <v>8</v>
       </c>
       <c r="Y24">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2717,13 +2717,13 @@
         <v>10</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
         <v>9</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2753,7 +2753,7 @@
         <v>10</v>
       </c>
       <c r="W25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X25">
         <v>9</v>
@@ -2794,13 +2794,13 @@
         <v>7</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L26">
         <v>6</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2830,7 +2830,7 @@
         <v>8</v>
       </c>
       <c r="W26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X26">
         <v>6</v>
@@ -2871,13 +2871,13 @@
         <v>10</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
         <v>9</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2913,7 +2913,7 @@
         <v>10</v>
       </c>
       <c r="Y27">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2945,16 +2945,16 @@
         <v>9</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L28">
         <v>5</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -3025,13 +3025,13 @@
         <v>10</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L29">
         <v>8</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -3067,7 +3067,7 @@
         <v>8</v>
       </c>
       <c r="Y29">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -3102,13 +3102,13 @@
         <v>8</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L30">
         <v>7</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3138,7 +3138,7 @@
         <v>8</v>
       </c>
       <c r="W30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X30">
         <v>8</v>
@@ -3179,13 +3179,13 @@
         <v>9</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L31">
         <v>7</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3215,13 +3215,13 @@
         <v>9</v>
       </c>
       <c r="W31">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X31">
         <v>7</v>
       </c>
       <c r="Y31">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3256,13 +3256,13 @@
         <v>8</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L32">
         <v>9</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3292,7 +3292,7 @@
         <v>8</v>
       </c>
       <c r="W32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X32">
         <v>9</v>
@@ -3333,13 +3333,13 @@
         <v>8</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L33">
         <v>8</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3375,7 +3375,7 @@
         <v>8</v>
       </c>
       <c r="Y33">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3410,13 +3410,13 @@
         <v>6</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L34">
         <v>7</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3487,13 +3487,13 @@
         <v>9</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L35">
         <v>7</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3523,7 +3523,7 @@
         <v>9</v>
       </c>
       <c r="W35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X35">
         <v>7</v>
@@ -3564,13 +3564,13 @@
         <v>6</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L36">
         <v>6</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3600,7 +3600,7 @@
         <v>6</v>
       </c>
       <c r="W36">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X36">
         <v>6</v>
@@ -3641,13 +3641,13 @@
         <v>7</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L37">
         <v>9</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3718,13 +3718,13 @@
         <v>5</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L38">
         <v>6</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3754,7 +3754,7 @@
         <v>6</v>
       </c>
       <c r="W38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X38">
         <v>6</v>
@@ -3795,13 +3795,13 @@
         <v>9</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L39">
         <v>10</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3831,7 +3831,7 @@
         <v>9</v>
       </c>
       <c r="W39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X39">
         <v>10</v>
@@ -3872,13 +3872,13 @@
         <v>9</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L40">
         <v>9</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N40">
         <v>-1</v>
@@ -3908,7 +3908,7 @@
         <v>9</v>
       </c>
       <c r="W40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X40">
         <v>9</v>
@@ -3949,13 +3949,13 @@
         <v>8</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L41">
         <v>7</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N41">
         <v>-1</v>
@@ -3985,13 +3985,13 @@
         <v>9</v>
       </c>
       <c r="W41">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X41">
         <v>7</v>
       </c>
       <c r="Y41">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -4026,13 +4026,13 @@
         <v>8</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L42">
         <v>8</v>
       </c>
       <c r="M42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N42">
         <v>-1</v>
@@ -4062,7 +4062,7 @@
         <v>9</v>
       </c>
       <c r="W42">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X42">
         <v>8</v>
@@ -4103,13 +4103,13 @@
         <v>5</v>
       </c>
       <c r="K43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L43">
         <v>6</v>
       </c>
       <c r="M43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N43">
         <v>-1</v>
@@ -4139,7 +4139,7 @@
         <v>5</v>
       </c>
       <c r="W43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X43">
         <v>6</v>
@@ -4180,13 +4180,13 @@
         <v>6</v>
       </c>
       <c r="K44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L44">
         <v>6</v>
       </c>
       <c r="M44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N44">
         <v>-1</v>
@@ -4216,13 +4216,13 @@
         <v>7</v>
       </c>
       <c r="W44">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X44">
         <v>7</v>
       </c>
       <c r="Y44">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:25">
@@ -4254,16 +4254,16 @@
         <v>5</v>
       </c>
       <c r="J45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L45">
         <v>7</v>
       </c>
       <c r="M45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N45">
         <v>-1</v>
@@ -4293,7 +4293,7 @@
         <v>5</v>
       </c>
       <c r="W45">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X45">
         <v>6</v>
@@ -4334,13 +4334,13 @@
         <v>8</v>
       </c>
       <c r="K46">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L46">
         <v>8</v>
       </c>
       <c r="M46">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N46">
         <v>-1</v>
@@ -4370,7 +4370,7 @@
         <v>9</v>
       </c>
       <c r="W46">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X46">
         <v>8</v>
@@ -4411,13 +4411,13 @@
         <v>9</v>
       </c>
       <c r="K47">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L47">
         <v>9</v>
       </c>
       <c r="M47">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N47">
         <v>-1</v>
@@ -4453,7 +4453,7 @@
         <v>9</v>
       </c>
       <c r="Y47">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -4530,7 +4530,7 @@
         <v>15.91</v>
       </c>
       <c r="H2">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4594,7 +4594,7 @@
         <v>4.55</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>8.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5519,7 +5519,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5551,22 +5551,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920337</v>
+        <v>22330051920098</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C2" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="D2" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5586,10 +5586,10 @@
         <v>159</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5597,16 +5597,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920340</v>
+        <v>22330051920121</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="D4" t="s">
-        <v>162</v>
+        <v>187</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -5620,16 +5620,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920119</v>
+        <v>22330051920121</v>
       </c>
       <c r="B5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C5" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D5" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -5638,6 +5638,52 @@
         <v>65</v>
       </c>
       <c r="G5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>22330051920337</v>
+      </c>
+      <c r="B6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" t="s">
+        <v>115</v>
+      </c>
+      <c r="D6" t="s">
+        <v>149</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>22330051920340</v>
+      </c>
+      <c r="B7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D7" t="s">
+        <v>162</v>
+      </c>
+      <c r="E7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" t="s">
+        <v>66</v>
+      </c>
+      <c r="G7">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1DM - Estadisticos 20221.xlsx
+++ b/grupos/1DM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="190">
   <si>
     <t>Materia</t>
   </si>
@@ -224,10 +224,10 @@
     <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
+    <t>Herrera Serrano Mayra Iliana</t>
+  </si>
+  <si>
     <t>Moreno Aroyo Anél</t>
-  </si>
-  <si>
-    <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
     <t>Rosas Aguilar Claudia Leonor</t>
@@ -1112,7 +1112,7 @@
         <v>-1</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -1189,7 +1189,7 @@
         <v>-1</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -1266,7 +1266,7 @@
         <v>-1</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1343,7 +1343,7 @@
         <v>-1</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1361,7 +1361,7 @@
         <v>6</v>
       </c>
       <c r="U7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V7">
         <v>6</v>
@@ -1420,7 +1420,7 @@
         <v>-1</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1438,7 +1438,7 @@
         <v>8</v>
       </c>
       <c r="U8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V8">
         <v>7</v>
@@ -1497,7 +1497,7 @@
         <v>-1</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1574,7 +1574,7 @@
         <v>-1</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1651,7 +1651,7 @@
         <v>-1</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1669,7 +1669,7 @@
         <v>7</v>
       </c>
       <c r="U11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V11">
         <v>8</v>
@@ -1728,7 +1728,7 @@
         <v>-1</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1805,7 +1805,7 @@
         <v>-1</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1882,7 +1882,7 @@
         <v>-1</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1959,7 +1959,7 @@
         <v>-1</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -2036,7 +2036,7 @@
         <v>-1</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -2113,7 +2113,7 @@
         <v>-1</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2190,7 +2190,7 @@
         <v>-1</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2208,7 +2208,7 @@
         <v>6</v>
       </c>
       <c r="U18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V18">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>-1</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2285,7 +2285,7 @@
         <v>6</v>
       </c>
       <c r="U19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V19">
         <v>5</v>
@@ -2344,7 +2344,7 @@
         <v>-1</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2421,7 +2421,7 @@
         <v>-1</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2498,7 +2498,7 @@
         <v>-1</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2575,7 +2575,7 @@
         <v>-1</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2593,7 +2593,7 @@
         <v>6</v>
       </c>
       <c r="U23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V23">
         <v>5</v>
@@ -2652,7 +2652,7 @@
         <v>-1</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2729,7 +2729,7 @@
         <v>-1</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2806,7 +2806,7 @@
         <v>-1</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2883,7 +2883,7 @@
         <v>-1</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -2960,7 +2960,7 @@
         <v>-1</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -3037,7 +3037,7 @@
         <v>-1</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -3114,7 +3114,7 @@
         <v>-1</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -3191,7 +3191,7 @@
         <v>-1</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -3209,7 +3209,7 @@
         <v>9</v>
       </c>
       <c r="U31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V31">
         <v>9</v>
@@ -3268,7 +3268,7 @@
         <v>-1</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -3345,7 +3345,7 @@
         <v>-1</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -3422,7 +3422,7 @@
         <v>-1</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P34">
         <v>-1</v>
@@ -3499,7 +3499,7 @@
         <v>-1</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P35">
         <v>-1</v>
@@ -3576,7 +3576,7 @@
         <v>-1</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P36">
         <v>-1</v>
@@ -3594,7 +3594,7 @@
         <v>6</v>
       </c>
       <c r="U36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V36">
         <v>6</v>
@@ -3653,7 +3653,7 @@
         <v>-1</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P37">
         <v>-1</v>
@@ -3730,7 +3730,7 @@
         <v>-1</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P38">
         <v>-1</v>
@@ -3748,7 +3748,7 @@
         <v>7</v>
       </c>
       <c r="U38">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V38">
         <v>6</v>
@@ -3807,7 +3807,7 @@
         <v>-1</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P39">
         <v>-1</v>
@@ -3884,7 +3884,7 @@
         <v>-1</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P40">
         <v>-1</v>
@@ -3961,7 +3961,7 @@
         <v>-1</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P41">
         <v>-1</v>
@@ -4038,7 +4038,7 @@
         <v>-1</v>
       </c>
       <c r="O42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P42">
         <v>-1</v>
@@ -4115,7 +4115,7 @@
         <v>-1</v>
       </c>
       <c r="O43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P43">
         <v>-1</v>
@@ -4133,7 +4133,7 @@
         <v>6</v>
       </c>
       <c r="U43">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V43">
         <v>5</v>
@@ -4192,7 +4192,7 @@
         <v>-1</v>
       </c>
       <c r="O44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P44">
         <v>-1</v>
@@ -4210,7 +4210,7 @@
         <v>8</v>
       </c>
       <c r="U44">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V44">
         <v>7</v>
@@ -4269,7 +4269,7 @@
         <v>-1</v>
       </c>
       <c r="O45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P45">
         <v>-1</v>
@@ -4346,7 +4346,7 @@
         <v>-1</v>
       </c>
       <c r="O46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P46">
         <v>-1</v>
@@ -4423,7 +4423,7 @@
         <v>-1</v>
       </c>
       <c r="O47">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P47">
         <v>-1</v>
@@ -4605,7 +4605,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>68</v>
@@ -4626,7 +4626,7 @@
         <v>4.55</v>
       </c>
       <c r="H5">
-        <v>9.1</v>
+        <v>7.3</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4637,7 +4637,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>69</v>
@@ -4646,19 +4646,19 @@
         <v>44</v>
       </c>
       <c r="D6">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>95.45</v>
+        <v>97.73</v>
       </c>
       <c r="G6">
-        <v>4.55</v>
+        <v>2.27</v>
       </c>
       <c r="H6">
-        <v>7.3</v>
+        <v>9.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5519,7 +5519,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5597,16 +5597,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920121</v>
+        <v>22330051920100</v>
       </c>
       <c r="B4" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="D4" t="s">
-        <v>187</v>
+        <v>164</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -5620,16 +5620,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920121</v>
+        <v>22330051920100</v>
       </c>
       <c r="B5" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="D5" t="s">
-        <v>187</v>
+        <v>164</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920337</v>
+        <v>22330051920121</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="C6" t="s">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="D6" t="s">
-        <v>149</v>
+        <v>187</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5666,24 +5666,70 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
+        <v>22330051920121</v>
+      </c>
+      <c r="B7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" t="s">
+        <v>143</v>
+      </c>
+      <c r="D7" t="s">
+        <v>187</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>65</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>22330051920337</v>
+      </c>
+      <c r="B8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" t="s">
+        <v>115</v>
+      </c>
+      <c r="D8" t="s">
+        <v>149</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" t="s">
+        <v>65</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
         <v>22330051920340</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B9" t="s">
         <v>86</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C9" t="s">
         <v>82</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D9" t="s">
         <v>162</v>
       </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="E9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" t="s">
         <v>66</v>
       </c>
-      <c r="G7">
+      <c r="G9">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1DM - Estadisticos 20221.xlsx
+++ b/grupos/1DM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="190">
   <si>
     <t>Materia</t>
   </si>
@@ -215,10 +215,10 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
     <t>González Altamirano Victorino Juventino</t>
-  </si>
-  <si>
-    <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
     <t>García Sánchez Magda Bexabe</t>
@@ -1109,7 +1109,7 @@
         <v>6</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
         <v>10</v>
@@ -1124,7 +1124,7 @@
         <v>-1</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T4">
         <v>9</v>
@@ -1186,7 +1186,7 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
         <v>10</v>
@@ -1201,7 +1201,7 @@
         <v>-1</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>9</v>
@@ -1263,7 +1263,7 @@
         <v>7</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O6">
         <v>10</v>
@@ -1278,7 +1278,7 @@
         <v>-1</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T6">
         <v>7</v>
@@ -1296,7 +1296,7 @@
         <v>7</v>
       </c>
       <c r="Y6">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1340,7 +1340,7 @@
         <v>5</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O7">
         <v>5</v>
@@ -1355,7 +1355,7 @@
         <v>-1</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
         <v>6</v>
@@ -1373,7 +1373,7 @@
         <v>7</v>
       </c>
       <c r="Y7">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1417,7 +1417,7 @@
         <v>7</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O8">
         <v>7</v>
@@ -1432,10 +1432,10 @@
         <v>-1</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U8">
         <v>8</v>
@@ -1494,7 +1494,7 @@
         <v>8</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
         <v>10</v>
@@ -1509,7 +1509,7 @@
         <v>-1</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T9">
         <v>9</v>
@@ -1571,7 +1571,7 @@
         <v>8</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O10">
         <v>10</v>
@@ -1586,7 +1586,7 @@
         <v>-1</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T10">
         <v>8</v>
@@ -1648,7 +1648,7 @@
         <v>5</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O11">
         <v>10</v>
@@ -1663,7 +1663,7 @@
         <v>-1</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T11">
         <v>7</v>
@@ -1725,7 +1725,7 @@
         <v>7</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O12">
         <v>10</v>
@@ -1740,10 +1740,10 @@
         <v>-1</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U12">
         <v>10</v>
@@ -1758,7 +1758,7 @@
         <v>8</v>
       </c>
       <c r="Y12">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1802,7 +1802,7 @@
         <v>7</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
         <v>10</v>
@@ -1817,7 +1817,7 @@
         <v>-1</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T13">
         <v>9</v>
@@ -1879,7 +1879,7 @@
         <v>7</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
         <v>10</v>
@@ -1894,7 +1894,7 @@
         <v>-1</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T14">
         <v>8</v>
@@ -1956,7 +1956,7 @@
         <v>7</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O15">
         <v>10</v>
@@ -1971,7 +1971,7 @@
         <v>-1</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T15">
         <v>7</v>
@@ -1989,7 +1989,7 @@
         <v>6</v>
       </c>
       <c r="Y15">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -2033,7 +2033,7 @@
         <v>7</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O16">
         <v>10</v>
@@ -2048,10 +2048,10 @@
         <v>-1</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U16">
         <v>10</v>
@@ -2110,7 +2110,7 @@
         <v>9</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O17">
         <v>10</v>
@@ -2125,7 +2125,7 @@
         <v>-1</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
         <v>9</v>
@@ -2187,7 +2187,7 @@
         <v>7</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O18">
         <v>7</v>
@@ -2202,7 +2202,7 @@
         <v>-1</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T18">
         <v>6</v>
@@ -2264,7 +2264,7 @@
         <v>5</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O19">
         <v>10</v>
@@ -2279,10 +2279,10 @@
         <v>-1</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U19">
         <v>8</v>
@@ -2297,7 +2297,7 @@
         <v>7</v>
       </c>
       <c r="Y19">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2341,7 +2341,7 @@
         <v>5</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O20">
         <v>6</v>
@@ -2356,7 +2356,7 @@
         <v>-1</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T20">
         <v>7</v>
@@ -2418,7 +2418,7 @@
         <v>6</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O21">
         <v>10</v>
@@ -2433,10 +2433,10 @@
         <v>-1</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U21">
         <v>8</v>
@@ -2495,7 +2495,7 @@
         <v>7</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O22">
         <v>10</v>
@@ -2510,10 +2510,10 @@
         <v>-1</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U22">
         <v>10</v>
@@ -2572,7 +2572,7 @@
         <v>6</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O23">
         <v>7</v>
@@ -2587,7 +2587,7 @@
         <v>-1</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T23">
         <v>6</v>
@@ -2649,7 +2649,7 @@
         <v>8</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
         <v>10</v>
@@ -2664,10 +2664,10 @@
         <v>-1</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U24">
         <v>10</v>
@@ -2726,7 +2726,7 @@
         <v>9</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
         <v>10</v>
@@ -2741,7 +2741,7 @@
         <v>-1</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>9</v>
@@ -2803,7 +2803,7 @@
         <v>7</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O26">
         <v>10</v>
@@ -2818,7 +2818,7 @@
         <v>-1</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T26">
         <v>8</v>
@@ -2880,7 +2880,7 @@
         <v>9</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
         <v>10</v>
@@ -2895,7 +2895,7 @@
         <v>-1</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
         <v>10</v>
@@ -2957,7 +2957,7 @@
         <v>5</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O28">
         <v>6</v>
@@ -2972,7 +2972,7 @@
         <v>-1</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T28">
         <v>6</v>
@@ -2990,7 +2990,7 @@
         <v>5</v>
       </c>
       <c r="Y28">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -3034,7 +3034,7 @@
         <v>9</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
         <v>10</v>
@@ -3049,7 +3049,7 @@
         <v>-1</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T29">
         <v>10</v>
@@ -3067,7 +3067,7 @@
         <v>8</v>
       </c>
       <c r="Y29">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -3111,7 +3111,7 @@
         <v>6</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O30">
         <v>10</v>
@@ -3126,7 +3126,7 @@
         <v>-1</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T30">
         <v>9</v>
@@ -3188,7 +3188,7 @@
         <v>8</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O31">
         <v>7</v>
@@ -3203,10 +3203,10 @@
         <v>-1</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U31">
         <v>9</v>
@@ -3221,7 +3221,7 @@
         <v>7</v>
       </c>
       <c r="Y31">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3265,7 +3265,7 @@
         <v>8</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O32">
         <v>10</v>
@@ -3280,7 +3280,7 @@
         <v>-1</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T32">
         <v>9</v>
@@ -3342,7 +3342,7 @@
         <v>8</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O33">
         <v>10</v>
@@ -3357,10 +3357,10 @@
         <v>-1</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U33">
         <v>10</v>
@@ -3419,7 +3419,7 @@
         <v>6</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O34">
         <v>10</v>
@@ -3434,7 +3434,7 @@
         <v>-1</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T34">
         <v>8</v>
@@ -3496,7 +3496,7 @@
         <v>6</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
         <v>10</v>
@@ -3511,7 +3511,7 @@
         <v>-1</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T35">
         <v>9</v>
@@ -3573,7 +3573,7 @@
         <v>6</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O36">
         <v>10</v>
@@ -3588,7 +3588,7 @@
         <v>-1</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T36">
         <v>6</v>
@@ -3606,7 +3606,7 @@
         <v>6</v>
       </c>
       <c r="Y36">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3650,7 +3650,7 @@
         <v>9</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O37">
         <v>10</v>
@@ -3665,7 +3665,7 @@
         <v>-1</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T37">
         <v>10</v>
@@ -3683,7 +3683,7 @@
         <v>8</v>
       </c>
       <c r="Y37">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3727,7 +3727,7 @@
         <v>7</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O38">
         <v>7</v>
@@ -3742,10 +3742,10 @@
         <v>-1</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U38">
         <v>8</v>
@@ -3804,7 +3804,7 @@
         <v>10</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O39">
         <v>10</v>
@@ -3819,7 +3819,7 @@
         <v>-1</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T39">
         <v>10</v>
@@ -3881,7 +3881,7 @@
         <v>8</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O40">
         <v>10</v>
@@ -3896,10 +3896,10 @@
         <v>-1</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U40">
         <v>10</v>
@@ -3914,7 +3914,7 @@
         <v>9</v>
       </c>
       <c r="Y40">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -3958,7 +3958,7 @@
         <v>8</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O41">
         <v>9</v>
@@ -3973,10 +3973,10 @@
         <v>-1</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U41">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>8</v>
       </c>
       <c r="N42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O42">
         <v>10</v>
@@ -4050,7 +4050,7 @@
         <v>-1</v>
       </c>
       <c r="S42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T42">
         <v>9</v>
@@ -4068,7 +4068,7 @@
         <v>8</v>
       </c>
       <c r="Y42">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43" spans="1:25">
@@ -4112,7 +4112,7 @@
         <v>5</v>
       </c>
       <c r="N43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O43">
         <v>10</v>
@@ -4127,7 +4127,7 @@
         <v>-1</v>
       </c>
       <c r="S43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T43">
         <v>6</v>
@@ -4145,7 +4145,7 @@
         <v>6</v>
       </c>
       <c r="Y43">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" spans="1:25">
@@ -4189,7 +4189,7 @@
         <v>8</v>
       </c>
       <c r="N44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O44">
         <v>7</v>
@@ -4204,7 +4204,7 @@
         <v>-1</v>
       </c>
       <c r="S44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T44">
         <v>8</v>
@@ -4266,7 +4266,7 @@
         <v>5</v>
       </c>
       <c r="N45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O45">
         <v>5</v>
@@ -4281,7 +4281,7 @@
         <v>-1</v>
       </c>
       <c r="S45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T45">
         <v>6</v>
@@ -4343,7 +4343,7 @@
         <v>8</v>
       </c>
       <c r="N46">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O46">
         <v>10</v>
@@ -4358,7 +4358,7 @@
         <v>-1</v>
       </c>
       <c r="S46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T46">
         <v>9</v>
@@ -4420,7 +4420,7 @@
         <v>8</v>
       </c>
       <c r="N47">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O47">
         <v>10</v>
@@ -4435,7 +4435,7 @@
         <v>-1</v>
       </c>
       <c r="S47">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T47">
         <v>10</v>
@@ -4509,7 +4509,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>65</v>
@@ -4518,19 +4518,19 @@
         <v>44</v>
       </c>
       <c r="D2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>84.09</v>
+        <v>86.36</v>
       </c>
       <c r="G2">
-        <v>15.91</v>
+        <v>13.64</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4541,7 +4541,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
@@ -4550,19 +4550,19 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>86.36</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="G3">
-        <v>13.64</v>
+        <v>6.82</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4690,7 +4690,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5519,7 +5519,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5551,22 +5551,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920098</v>
+        <v>22330051920100</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D2" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5574,22 +5574,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920098</v>
+        <v>22330051920100</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D3" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920100</v>
+        <v>22330051920105</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C4" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D4" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5620,22 +5620,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920100</v>
+        <v>22330051920105</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C5" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D5" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920121</v>
+        <v>22330051920098</v>
       </c>
       <c r="B6" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="C6" t="s">
-        <v>143</v>
+        <v>122</v>
       </c>
       <c r="D6" t="s">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5666,19 +5666,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920121</v>
+        <v>22330051920340</v>
       </c>
       <c r="B7" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="C7" t="s">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="D7" t="s">
-        <v>187</v>
+        <v>162</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
         <v>65</v>
@@ -5689,47 +5689,24 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920337</v>
+        <v>22330051920121</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="C8" t="s">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="D8" t="s">
-        <v>149</v>
+        <v>187</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
         <v>65</v>
       </c>
       <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920340</v>
-      </c>
-      <c r="B9" t="s">
-        <v>86</v>
-      </c>
-      <c r="C9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D9" t="s">
-        <v>162</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" t="s">
-        <v>66</v>
-      </c>
-      <c r="G9">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1DM - Estadisticos 20221.xlsx
+++ b/grupos/1DM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="190">
   <si>
     <t>Materia</t>
   </si>
@@ -1115,7 +1115,7 @@
         <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q4">
         <v>-1</v>
@@ -1133,7 +1133,7 @@
         <v>10</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W4">
         <v>9</v>
@@ -1192,7 +1192,7 @@
         <v>10</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
         <v>-1</v>
@@ -1269,7 +1269,7 @@
         <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q6">
         <v>-1</v>
@@ -1346,7 +1346,7 @@
         <v>5</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q7">
         <v>-1</v>
@@ -1364,7 +1364,7 @@
         <v>6</v>
       </c>
       <c r="V7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W7">
         <v>8</v>
@@ -1423,7 +1423,7 @@
         <v>7</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q8">
         <v>-1</v>
@@ -1500,7 +1500,7 @@
         <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q9">
         <v>-1</v>
@@ -1577,7 +1577,7 @@
         <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
         <v>-1</v>
@@ -1654,7 +1654,7 @@
         <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q11">
         <v>-1</v>
@@ -1672,7 +1672,7 @@
         <v>7</v>
       </c>
       <c r="V11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W11">
         <v>5</v>
@@ -1731,7 +1731,7 @@
         <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q12">
         <v>-1</v>
@@ -1749,7 +1749,7 @@
         <v>10</v>
       </c>
       <c r="V12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W12">
         <v>10</v>
@@ -1808,7 +1808,7 @@
         <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
         <v>-1</v>
@@ -1885,7 +1885,7 @@
         <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q14">
         <v>-1</v>
@@ -1962,7 +1962,7 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q15">
         <v>-1</v>
@@ -1980,7 +1980,7 @@
         <v>10</v>
       </c>
       <c r="V15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W15">
         <v>9</v>
@@ -2039,7 +2039,7 @@
         <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q16">
         <v>-1</v>
@@ -2116,7 +2116,7 @@
         <v>10</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q17">
         <v>-1</v>
@@ -2193,7 +2193,7 @@
         <v>7</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
         <v>-1</v>
@@ -2270,7 +2270,7 @@
         <v>10</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
         <v>-1</v>
@@ -2288,7 +2288,7 @@
         <v>8</v>
       </c>
       <c r="V19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W19">
         <v>7</v>
@@ -2347,7 +2347,7 @@
         <v>6</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q20">
         <v>-1</v>
@@ -2365,7 +2365,7 @@
         <v>7</v>
       </c>
       <c r="V20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W20">
         <v>7</v>
@@ -2424,7 +2424,7 @@
         <v>10</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q21">
         <v>-1</v>
@@ -2501,7 +2501,7 @@
         <v>10</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
         <v>-1</v>
@@ -2519,7 +2519,7 @@
         <v>10</v>
       </c>
       <c r="V22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W22">
         <v>10</v>
@@ -2578,7 +2578,7 @@
         <v>7</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q23">
         <v>-1</v>
@@ -2655,7 +2655,7 @@
         <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q24">
         <v>-1</v>
@@ -2732,7 +2732,7 @@
         <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
         <v>-1</v>
@@ -2809,7 +2809,7 @@
         <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
         <v>-1</v>
@@ -2886,7 +2886,7 @@
         <v>10</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
         <v>-1</v>
@@ -2963,7 +2963,7 @@
         <v>6</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q28">
         <v>-1</v>
@@ -2981,7 +2981,7 @@
         <v>7</v>
       </c>
       <c r="V28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W28">
         <v>6</v>
@@ -3040,7 +3040,7 @@
         <v>10</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q29">
         <v>-1</v>
@@ -3058,7 +3058,7 @@
         <v>10</v>
       </c>
       <c r="V29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W29">
         <v>10</v>
@@ -3117,7 +3117,7 @@
         <v>10</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q30">
         <v>-1</v>
@@ -3135,7 +3135,7 @@
         <v>10</v>
       </c>
       <c r="V30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W30">
         <v>10</v>
@@ -3194,7 +3194,7 @@
         <v>7</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q31">
         <v>-1</v>
@@ -3271,7 +3271,7 @@
         <v>10</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q32">
         <v>-1</v>
@@ -3348,7 +3348,7 @@
         <v>10</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q33">
         <v>-1</v>
@@ -3366,7 +3366,7 @@
         <v>10</v>
       </c>
       <c r="V33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W33">
         <v>10</v>
@@ -3425,7 +3425,7 @@
         <v>10</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q34">
         <v>-1</v>
@@ -3502,7 +3502,7 @@
         <v>10</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q35">
         <v>-1</v>
@@ -3579,7 +3579,7 @@
         <v>10</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q36">
         <v>-1</v>
@@ -3597,7 +3597,7 @@
         <v>9</v>
       </c>
       <c r="V36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W36">
         <v>8</v>
@@ -3656,7 +3656,7 @@
         <v>10</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q37">
         <v>-1</v>
@@ -3733,7 +3733,7 @@
         <v>7</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q38">
         <v>-1</v>
@@ -3810,7 +3810,7 @@
         <v>10</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q39">
         <v>-1</v>
@@ -3887,7 +3887,7 @@
         <v>10</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q40">
         <v>-1</v>
@@ -3964,7 +3964,7 @@
         <v>9</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q41">
         <v>-1</v>
@@ -3982,7 +3982,7 @@
         <v>8</v>
       </c>
       <c r="V41">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W41">
         <v>8</v>
@@ -4041,7 +4041,7 @@
         <v>10</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q42">
         <v>-1</v>
@@ -4118,7 +4118,7 @@
         <v>10</v>
       </c>
       <c r="P43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q43">
         <v>-1</v>
@@ -4136,7 +4136,7 @@
         <v>8</v>
       </c>
       <c r="V43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W43">
         <v>6</v>
@@ -4195,7 +4195,7 @@
         <v>7</v>
       </c>
       <c r="P44">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q44">
         <v>-1</v>
@@ -4213,7 +4213,7 @@
         <v>9</v>
       </c>
       <c r="V44">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W44">
         <v>8</v>
@@ -4272,7 +4272,7 @@
         <v>5</v>
       </c>
       <c r="P45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q45">
         <v>-1</v>
@@ -4349,7 +4349,7 @@
         <v>10</v>
       </c>
       <c r="P46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q46">
         <v>-1</v>
@@ -4426,7 +4426,7 @@
         <v>10</v>
       </c>
       <c r="P47">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q47">
         <v>-1</v>
@@ -4518,19 +4518,19 @@
         <v>44</v>
       </c>
       <c r="D2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>86.36</v>
+        <v>90.91</v>
       </c>
       <c r="G2">
-        <v>13.64</v>
+        <v>9.09</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5519,7 +5519,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5597,16 +5597,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920105</v>
+        <v>22330051920337</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="D4" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -5620,22 +5620,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920105</v>
+        <v>22330051920340</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s">
-        <v>129</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5643,70 +5643,24 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920098</v>
+        <v>22330051920105</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="C6" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="D6" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920340</v>
-      </c>
-      <c r="B7" t="s">
-        <v>86</v>
-      </c>
-      <c r="C7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D7" t="s">
-        <v>162</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>65</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920121</v>
-      </c>
-      <c r="B8" t="s">
-        <v>109</v>
-      </c>
-      <c r="C8" t="s">
-        <v>143</v>
-      </c>
-      <c r="D8" t="s">
-        <v>187</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>65</v>
-      </c>
-      <c r="G8">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1DM - Estadisticos 20221.xlsx
+++ b/grupos/1DM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="190">
   <si>
     <t>Materia</t>
   </si>
@@ -224,10 +224,10 @@
     <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
+    <t>Moreno Aroyo Anél</t>
+  </si>
+  <si>
     <t>Herrera Serrano Mayra Iliana</t>
-  </si>
-  <si>
-    <t>Moreno Aroyo Anél</t>
   </si>
   <si>
     <t>Rosas Aguilar Claudia Leonor</t>
@@ -1121,7 +1121,7 @@
         <v>-1</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S4">
         <v>8</v>
@@ -1198,7 +1198,7 @@
         <v>-1</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S5">
         <v>10</v>
@@ -1275,7 +1275,7 @@
         <v>-1</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S6">
         <v>6</v>
@@ -1352,7 +1352,7 @@
         <v>-1</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S7">
         <v>8</v>
@@ -1370,7 +1370,7 @@
         <v>8</v>
       </c>
       <c r="X7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y7">
         <v>6</v>
@@ -1429,7 +1429,7 @@
         <v>-1</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S8">
         <v>7</v>
@@ -1447,7 +1447,7 @@
         <v>9</v>
       </c>
       <c r="X8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y8">
         <v>7</v>
@@ -1506,7 +1506,7 @@
         <v>-1</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
         <v>9</v>
@@ -1524,7 +1524,7 @@
         <v>10</v>
       </c>
       <c r="X9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y9">
         <v>8</v>
@@ -1583,7 +1583,7 @@
         <v>-1</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S10">
         <v>7</v>
@@ -1601,7 +1601,7 @@
         <v>10</v>
       </c>
       <c r="X10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y10">
         <v>8</v>
@@ -1660,7 +1660,7 @@
         <v>-1</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S11">
         <v>5</v>
@@ -1678,7 +1678,7 @@
         <v>5</v>
       </c>
       <c r="X11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y11">
         <v>5</v>
@@ -1737,7 +1737,7 @@
         <v>-1</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S12">
         <v>6</v>
@@ -1814,7 +1814,7 @@
         <v>-1</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
         <v>6</v>
@@ -1891,7 +1891,7 @@
         <v>-1</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S14">
         <v>7</v>
@@ -1968,7 +1968,7 @@
         <v>-1</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S15">
         <v>6</v>
@@ -2045,7 +2045,7 @@
         <v>-1</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S16">
         <v>7</v>
@@ -2122,7 +2122,7 @@
         <v>-1</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S17">
         <v>10</v>
@@ -2199,7 +2199,7 @@
         <v>-1</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S18">
         <v>7</v>
@@ -2276,7 +2276,7 @@
         <v>-1</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S19">
         <v>7</v>
@@ -2294,7 +2294,7 @@
         <v>7</v>
       </c>
       <c r="X19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y19">
         <v>6</v>
@@ -2353,7 +2353,7 @@
         <v>-1</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S20">
         <v>6</v>
@@ -2371,7 +2371,7 @@
         <v>7</v>
       </c>
       <c r="X20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y20">
         <v>6</v>
@@ -2430,7 +2430,7 @@
         <v>-1</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S21">
         <v>6</v>
@@ -2507,7 +2507,7 @@
         <v>-1</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S22">
         <v>8</v>
@@ -2584,7 +2584,7 @@
         <v>-1</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S23">
         <v>5</v>
@@ -2661,7 +2661,7 @@
         <v>-1</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S24">
         <v>10</v>
@@ -2738,7 +2738,7 @@
         <v>-1</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
         <v>10</v>
@@ -2815,7 +2815,7 @@
         <v>-1</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S26">
         <v>8</v>
@@ -2892,7 +2892,7 @@
         <v>-1</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
         <v>10</v>
@@ -2969,7 +2969,7 @@
         <v>-1</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S28">
         <v>8</v>
@@ -2987,7 +2987,7 @@
         <v>6</v>
       </c>
       <c r="X28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y28">
         <v>6</v>
@@ -3046,7 +3046,7 @@
         <v>-1</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S29">
         <v>8</v>
@@ -3123,7 +3123,7 @@
         <v>-1</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S30">
         <v>7</v>
@@ -3141,7 +3141,7 @@
         <v>10</v>
       </c>
       <c r="X30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y30">
         <v>6</v>
@@ -3200,7 +3200,7 @@
         <v>-1</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S31">
         <v>9</v>
@@ -3218,7 +3218,7 @@
         <v>8</v>
       </c>
       <c r="X31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y31">
         <v>8</v>
@@ -3277,7 +3277,7 @@
         <v>-1</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
         <v>7</v>
@@ -3354,7 +3354,7 @@
         <v>-1</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S33">
         <v>9</v>
@@ -3431,7 +3431,7 @@
         <v>-1</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S34">
         <v>7</v>
@@ -3508,7 +3508,7 @@
         <v>-1</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S35">
         <v>8</v>
@@ -3585,7 +3585,7 @@
         <v>-1</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S36">
         <v>6</v>
@@ -3662,7 +3662,7 @@
         <v>-1</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S37">
         <v>6</v>
@@ -3739,7 +3739,7 @@
         <v>-1</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S38">
         <v>6</v>
@@ -3816,7 +3816,7 @@
         <v>-1</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S39">
         <v>10</v>
@@ -3893,7 +3893,7 @@
         <v>-1</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S40">
         <v>8</v>
@@ -3970,7 +3970,7 @@
         <v>-1</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S41">
         <v>7</v>
@@ -4047,7 +4047,7 @@
         <v>-1</v>
       </c>
       <c r="R42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S42">
         <v>10</v>
@@ -4065,7 +4065,7 @@
         <v>10</v>
       </c>
       <c r="X42">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y42">
         <v>9</v>
@@ -4124,7 +4124,7 @@
         <v>-1</v>
       </c>
       <c r="R43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S43">
         <v>8</v>
@@ -4201,7 +4201,7 @@
         <v>-1</v>
       </c>
       <c r="R44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S44">
         <v>8</v>
@@ -4219,7 +4219,7 @@
         <v>8</v>
       </c>
       <c r="X44">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y44">
         <v>8</v>
@@ -4278,7 +4278,7 @@
         <v>-1</v>
       </c>
       <c r="R45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S45">
         <v>5</v>
@@ -4296,7 +4296,7 @@
         <v>5</v>
       </c>
       <c r="X45">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y45">
         <v>5</v>
@@ -4355,7 +4355,7 @@
         <v>-1</v>
       </c>
       <c r="R46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S46">
         <v>10</v>
@@ -4373,7 +4373,7 @@
         <v>9</v>
       </c>
       <c r="X46">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y46">
         <v>9</v>
@@ -4432,7 +4432,7 @@
         <v>-1</v>
       </c>
       <c r="R47">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S47">
         <v>10</v>
@@ -4605,7 +4605,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>68</v>
@@ -4614,19 +4614,19 @@
         <v>44</v>
       </c>
       <c r="D5">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>95.45</v>
+        <v>97.73</v>
       </c>
       <c r="G5">
-        <v>4.55</v>
+        <v>2.27</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>9.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4637,7 +4637,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>69</v>
@@ -4658,7 +4658,7 @@
         <v>2.27</v>
       </c>
       <c r="H6">
-        <v>9.1</v>
+        <v>7.3</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5519,7 +5519,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5551,22 +5551,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920100</v>
+        <v>22330051920091</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
-        <v>125</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5574,16 +5574,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920100</v>
+        <v>22330051920091</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
-        <v>125</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -5597,16 +5597,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920337</v>
+        <v>22330051920100</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="D4" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -5620,22 +5620,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920340</v>
+        <v>22330051920100</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>125</v>
       </c>
       <c r="D5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5643,24 +5643,47 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920105</v>
+        <v>22330051920337</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="D6" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>22330051920340</v>
+      </c>
+      <c r="B7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D7" t="s">
+        <v>162</v>
+      </c>
+      <c r="E7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" t="s">
+        <v>65</v>
+      </c>
+      <c r="G7">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1DM - Estadisticos 20221.xlsx
+++ b/grupos/1DM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="190">
   <si>
     <t>Materia</t>
   </si>
@@ -1118,7 +1118,7 @@
         <v>6</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R4">
         <v>7</v>
@@ -1195,7 +1195,7 @@
         <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R5">
         <v>8</v>
@@ -1272,7 +1272,7 @@
         <v>7</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R6">
         <v>6</v>
@@ -1349,7 +1349,7 @@
         <v>5</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R7">
         <v>6</v>
@@ -1367,7 +1367,7 @@
         <v>5</v>
       </c>
       <c r="W7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X7">
         <v>6</v>
@@ -1426,7 +1426,7 @@
         <v>6</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
         <v>5</v>
@@ -1503,7 +1503,7 @@
         <v>9</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R9">
         <v>10</v>
@@ -1580,7 +1580,7 @@
         <v>10</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>5</v>
@@ -1657,7 +1657,7 @@
         <v>5</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
         <v>9</v>
@@ -1675,7 +1675,7 @@
         <v>7</v>
       </c>
       <c r="W11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X11">
         <v>7</v>
@@ -1734,7 +1734,7 @@
         <v>9</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
         <v>9</v>
@@ -1811,7 +1811,7 @@
         <v>8</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
         <v>8</v>
@@ -1888,7 +1888,7 @@
         <v>9</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R14">
         <v>7</v>
@@ -1906,7 +1906,7 @@
         <v>8</v>
       </c>
       <c r="W14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X14">
         <v>6</v>
@@ -1965,7 +1965,7 @@
         <v>6</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
         <v>6</v>
@@ -2042,7 +2042,7 @@
         <v>9</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
         <v>9</v>
@@ -2119,7 +2119,7 @@
         <v>9</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
         <v>9</v>
@@ -2137,7 +2137,7 @@
         <v>8</v>
       </c>
       <c r="W17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X17">
         <v>8</v>
@@ -2196,7 +2196,7 @@
         <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R18">
         <v>7</v>
@@ -2273,7 +2273,7 @@
         <v>9</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>5</v>
@@ -2291,7 +2291,7 @@
         <v>7</v>
       </c>
       <c r="W19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>6</v>
@@ -2350,7 +2350,7 @@
         <v>5</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R20">
         <v>6</v>
@@ -2427,7 +2427,7 @@
         <v>5</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
         <v>7</v>
@@ -2504,7 +2504,7 @@
         <v>8</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R22">
         <v>9</v>
@@ -2522,7 +2522,7 @@
         <v>8</v>
       </c>
       <c r="W22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X22">
         <v>9</v>
@@ -2581,7 +2581,7 @@
         <v>5</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R23">
         <v>6</v>
@@ -2599,7 +2599,7 @@
         <v>5</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X23">
         <v>6</v>
@@ -2658,7 +2658,7 @@
         <v>9</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
         <v>9</v>
@@ -2735,7 +2735,7 @@
         <v>10</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>10</v>
@@ -2812,7 +2812,7 @@
         <v>8</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R26">
         <v>7</v>
@@ -2889,7 +2889,7 @@
         <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
         <v>10</v>
@@ -2966,7 +2966,7 @@
         <v>8</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
         <v>8</v>
@@ -2984,7 +2984,7 @@
         <v>6</v>
       </c>
       <c r="W28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X28">
         <v>6</v>
@@ -3043,7 +3043,7 @@
         <v>9</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
         <v>9</v>
@@ -3120,7 +3120,7 @@
         <v>7</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R30">
         <v>6</v>
@@ -3138,7 +3138,7 @@
         <v>7</v>
       </c>
       <c r="W30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X30">
         <v>7</v>
@@ -3197,7 +3197,7 @@
         <v>9</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
         <v>9</v>
@@ -3215,7 +3215,7 @@
         <v>9</v>
       </c>
       <c r="W31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X31">
         <v>8</v>
@@ -3274,7 +3274,7 @@
         <v>9</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
         <v>10</v>
@@ -3351,7 +3351,7 @@
         <v>8</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
         <v>9</v>
@@ -3428,7 +3428,7 @@
         <v>7</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
         <v>8</v>
@@ -3505,7 +3505,7 @@
         <v>9</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
         <v>8</v>
@@ -3582,7 +3582,7 @@
         <v>8</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R36">
         <v>6</v>
@@ -3600,7 +3600,7 @@
         <v>7</v>
       </c>
       <c r="W36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X36">
         <v>6</v>
@@ -3659,7 +3659,7 @@
         <v>9</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R37">
         <v>9</v>
@@ -3736,7 +3736,7 @@
         <v>7</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R38">
         <v>6</v>
@@ -3813,7 +3813,7 @@
         <v>10</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R39">
         <v>10</v>
@@ -3890,7 +3890,7 @@
         <v>8</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R40">
         <v>8</v>
@@ -3967,7 +3967,7 @@
         <v>6</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R41">
         <v>7</v>
@@ -4044,7 +4044,7 @@
         <v>10</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R42">
         <v>10</v>
@@ -4121,7 +4121,7 @@
         <v>7</v>
       </c>
       <c r="Q43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R43">
         <v>7</v>
@@ -4139,7 +4139,7 @@
         <v>6</v>
       </c>
       <c r="W43">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X43">
         <v>6</v>
@@ -4198,7 +4198,7 @@
         <v>5</v>
       </c>
       <c r="Q44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R44">
         <v>6</v>
@@ -4275,7 +4275,7 @@
         <v>5</v>
       </c>
       <c r="Q45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R45">
         <v>5</v>
@@ -4352,7 +4352,7 @@
         <v>10</v>
       </c>
       <c r="Q46">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R46">
         <v>10</v>
@@ -4429,7 +4429,7 @@
         <v>10</v>
       </c>
       <c r="Q47">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R47">
         <v>10</v>
@@ -5519,7 +5519,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5551,22 +5551,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920091</v>
+        <v>22330051920337</v>
       </c>
       <c r="B2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="D2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5597,16 +5597,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920100</v>
+        <v>22330051920340</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -5615,75 +5615,6 @@
         <v>65</v>
       </c>
       <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920100</v>
-      </c>
-      <c r="B5" t="s">
-        <v>88</v>
-      </c>
-      <c r="C5" t="s">
-        <v>125</v>
-      </c>
-      <c r="D5" t="s">
-        <v>164</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>66</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920337</v>
-      </c>
-      <c r="B6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" t="s">
-        <v>115</v>
-      </c>
-      <c r="D6" t="s">
-        <v>149</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>65</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920340</v>
-      </c>
-      <c r="B7" t="s">
-        <v>86</v>
-      </c>
-      <c r="C7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D7" t="s">
-        <v>162</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>65</v>
-      </c>
-      <c r="G7">
         <v>5</v>
       </c>
     </row>
